--- a/output/graficos_educacion_tasas/comunal_e_mat_a_2024_atacama.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_mat_a_2024_atacama.xlsx
@@ -60,7 +60,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:51</t>
+    <t xml:space="preserve">2026-09-09 20:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_mat_a_2024_atacama.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_mat_a_2024_atacama.xlsx
@@ -24,33 +24,33 @@
     <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
+    <t xml:space="preserve">Copiapó</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caldera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tierra Amarilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chañaral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diego de Almagro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vallenar</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alto del Carmen</t>
   </si>
   <si>
-    <t xml:space="preserve">Caldera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chañaral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Copiapó</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diego de Almagro</t>
-  </si>
-  <si>
     <t xml:space="preserve">Freirina</t>
   </si>
   <si>
     <t xml:space="preserve">Huasco</t>
   </si>
   <si>
-    <t xml:space="preserve">Tierra Amarilla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vallenar</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -60,7 +60,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:58</t>
+    <t xml:space="preserve">2026-09-18 10:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -472,7 +472,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>75.36</v>
+        <v>77.38</v>
       </c>
     </row>
     <row r="3">
@@ -488,7 +488,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>78.71</v>
+        <v>74.22</v>
       </c>
     </row>
     <row r="5">
@@ -496,7 +496,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>77.38</v>
+        <v>78.71</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>78.83</v>
+        <v>78.7</v>
       </c>
     </row>
     <row r="8">
@@ -520,7 +520,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>77.74</v>
+        <v>75.36</v>
       </c>
     </row>
     <row r="9">
@@ -528,7 +528,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>74.22</v>
+        <v>78.83</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>78.7</v>
+        <v>77.74</v>
       </c>
     </row>
   </sheetData>
